--- a/survey_templates/039_response_content_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/039_response_content_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How clear is this response?</t>
+          <t>Question5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your feedback about this response?</t>
+          <t>Question10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rate your satisfaction with this response</t>
+          <t>Question24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rate your impression with this response</t>
+          <t>Question25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1165,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,63 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
